--- a/ss06_2210_MLModel/ML_PonitPlus.xlsx
+++ b/ss06_2210_MLModel/ML_PonitPlus.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\ML_K23416\ss06_2210_MLModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FEEE23-6A5A-4B29-A122-15051D0DCB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34951C93-029F-47A8-8794-2C87947B0C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VD3" sheetId="1" r:id="rId1"/>
+    <sheet name="Office" sheetId="3" r:id="rId1"/>
     <sheet name="Bài làm" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,16 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
-  <si>
-    <t>Color</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
   <si>
     <t>x0</t>
   </si>
@@ -105,12 +96,15 @@
   <si>
     <t>y</t>
   </si>
+  <si>
+    <t>x4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,21 +120,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF656565"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -153,7 +173,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,6 +191,1052 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="vi-VN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Office!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Office!$E$2:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.91</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.23</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.04</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.64</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>29.64</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>33.520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>33.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>42.89</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48.87</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>58.45</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>61.69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1D89-4CF8-B0BF-F60DE4AFA870}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Office!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Predicted Price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Office!$V$2:$V$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>-2.9873653592703917</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2190383499989954</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0509863555099717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0460183749668479</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.9714004461542274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4794413715597639</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0425435495602287</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12.213763941518863</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.58154827798251</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.098462726583833</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>28.452671507716108</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.437149817828164</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.872762605887885</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>34.687532957624349</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34.501474834117069</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>34.562469335144868</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43.405667549512252</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48.725261946269441</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>56.387018260658849</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>57.972153150676007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1D89-4CF8-B0BF-F60DE4AFA870}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1772894239"/>
+        <c:axId val="1772903359"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1772894239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="vi-VN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1772903359"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1772903359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="vi-VN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1772894239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="vi-VN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="vi-VN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>642938</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>166688</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{949B8186-11B5-F409-5CD5-E26737F98400}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,513 +1501,1170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D815C7E-EC0C-4FF1-8044-766FFB2AF152}">
+  <dimension ref="A1:W24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="15.5" customWidth="1"/>
-    <col min="17" max="17" width="14.59765625" customWidth="1"/>
+    <col min="11" max="11" width="8.796875" customWidth="1"/>
+    <col min="19" max="19" width="13.796875" customWidth="1"/>
+    <col min="22" max="22" width="16.296875" customWidth="1"/>
+    <col min="23" max="23" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" cm="1">
+        <f t="array" ref="O1:T6">MMULT(TRANSPOSE(G2:L21),G2:L21)</f>
+        <v>20</v>
+      </c>
+      <c r="P1" s="1">
+        <v>50.839999999999996</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>435.64000000000004</v>
+      </c>
+      <c r="R1" s="1">
+        <v>11.029999999999998</v>
+      </c>
+      <c r="S1" s="1">
+        <v>282</v>
+      </c>
+      <c r="T1">
+        <v>467.71999999999997</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="W1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="B2" s="3">
+        <v>11.21</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.53</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="I2" s="3">
+        <v>11.21</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.53</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50.839999999999996</v>
+      </c>
+      <c r="P2" s="1">
+        <v>228.66939999999994</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>991.42409999999995</v>
+      </c>
+      <c r="R2" s="1">
+        <v>26.494300000000003</v>
+      </c>
+      <c r="S2" s="1">
+        <v>653.90499999999997</v>
+      </c>
+      <c r="T2">
+        <v>1023.8301</v>
+      </c>
+      <c r="V2">
+        <f>$R$14+$R$15*H2+$R$16*I2+$R$17*J2+$R$18*K2</f>
+        <v>-2.9873653592703917</v>
+      </c>
+      <c r="W2">
+        <f>POWER(L2-V2,2)</f>
+        <v>9.1649410185103477</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="B3" s="3">
+        <v>63.46</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="E3" s="3">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="I3" s="3">
+        <v>63.46</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="K3" s="3">
+        <v>2</v>
+      </c>
+      <c r="L3" s="3">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="O3" s="1">
+        <v>435.64000000000004</v>
+      </c>
+      <c r="P3" s="1">
+        <v>991.42409999999995</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>15643.789200000005</v>
+      </c>
+      <c r="R3" s="1">
+        <v>222.99349999999998</v>
+      </c>
+      <c r="S3" s="1">
+        <v>5454.42</v>
+      </c>
+      <c r="T3">
+        <v>9043.8549000000003</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V21" si="0">$R$14+$R$15*H3+$R$16*I3+$R$17*J3+$R$18*K3</f>
+        <v>2.2190383499989954</v>
+      </c>
+      <c r="W3">
+        <f t="shared" ref="W3:W21" si="1">POWER(L3-V3,2)</f>
+        <v>2.2212429770423103E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3">
+        <v>48.25</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="K1" s="1" cm="1">
-        <f t="array" ref="K1:N4">MMULT(TRANSPOSE(E2:H12),E2:H12)</f>
+      <c r="E4" s="3">
+        <v>4.18</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>48.25</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="K4" s="3">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3">
+        <v>4.18</v>
+      </c>
+      <c r="O4" s="1">
+        <v>11.029999999999998</v>
+      </c>
+      <c r="P4" s="1">
+        <v>26.494300000000003</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>222.99349999999998</v>
+      </c>
+      <c r="R4" s="1">
+        <v>7.5642999999999985</v>
+      </c>
+      <c r="S4" s="1">
+        <v>172.33999999999997</v>
+      </c>
+      <c r="T4">
+        <v>287.65010000000001</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="0"/>
+        <v>5.0509863555099717</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="1"/>
+        <v>0.75861723148454319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3.93</v>
+      </c>
+      <c r="B5" s="3">
+        <v>21.56</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4.63</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3.93</v>
+      </c>
+      <c r="I5" s="3">
+        <v>21.56</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="K5" s="3">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3">
+        <v>4.63</v>
+      </c>
+      <c r="O5" s="1">
+        <v>282</v>
+      </c>
+      <c r="P5" s="1">
+        <v>653.90499999999997</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>5454.42</v>
+      </c>
+      <c r="R5" s="1">
+        <v>172.33999999999997</v>
+      </c>
+      <c r="S5" s="1">
+        <v>5725.5</v>
+      </c>
+      <c r="T5">
+        <v>10039.504999999999</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="0"/>
+        <v>3.0460183749668479</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="1"/>
+        <v>2.5089977884426649</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="B6" s="3">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6.57</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="K6" s="3">
+        <v>5</v>
+      </c>
+      <c r="L6" s="3">
+        <v>6.57</v>
+      </c>
+      <c r="O6">
+        <v>467.71999999999997</v>
+      </c>
+      <c r="P6">
+        <v>1023.8301</v>
+      </c>
+      <c r="Q6">
+        <v>9043.8549000000003</v>
+      </c>
+      <c r="R6">
+        <v>287.65010000000001</v>
+      </c>
+      <c r="S6">
+        <v>10039.504999999999</v>
+      </c>
+      <c r="T6">
+        <v>17814.938000000002</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="0"/>
+        <v>5.9714004461542274</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="1"/>
+        <v>0.35832142586435839</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3.58</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11.13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6.91</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3.58</v>
+      </c>
+      <c r="I7" s="3">
+        <v>11.13</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
+      <c r="L7" s="3">
+        <v>6.91</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="0"/>
+        <v>5.4794413715597639</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="1"/>
+        <v>2.0464979894048101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="B8" s="3">
+        <v>44.38</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9.23</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="I8" s="3">
+        <v>44.38</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="K8" s="3">
+        <v>7</v>
+      </c>
+      <c r="L8" s="3">
+        <v>9.23</v>
+      </c>
+      <c r="N8" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" cm="1">
+        <f t="array" ref="O8:S12">MINVERSE(O1:S5)</f>
+        <v>0.64114457070884145</v>
+      </c>
+      <c r="P8">
+        <v>-4.4549650114809818E-2</v>
+      </c>
+      <c r="Q8">
+        <v>-6.4316451660924381E-3</v>
+      </c>
+      <c r="R8">
+        <v>-0.39880209109482428</v>
+      </c>
+      <c r="S8">
+        <v>-8.3592845298137586E-3</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>9.0425435495602287</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="1"/>
+        <v>3.5139920811478612E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>3.81</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="D9" s="3">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3.81</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="K9" s="3">
+        <v>9</v>
+      </c>
+      <c r="L9" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="O9">
+        <v>-4.4549650114809811E-2</v>
+      </c>
+      <c r="P9">
+        <v>1.078653632977843E-2</v>
+      </c>
+      <c r="Q9">
+        <v>2.7590140774220193E-4</v>
+      </c>
+      <c r="R9">
+        <v>9.9007508855368902E-3</v>
+      </c>
+      <c r="S9">
+        <v>4.0144157359566093E-4</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="0"/>
+        <v>12.213763941518863</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="1"/>
+        <v>0.66221175251631492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>5.71</v>
+      </c>
+      <c r="B10" s="3">
+        <v>42.28</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12.04</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5.71</v>
+      </c>
+      <c r="I10" s="3">
+        <v>42.28</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="K10" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="L10" s="3">
+        <v>12.04</v>
+      </c>
+      <c r="O10">
+        <v>-6.4316451660924364E-3</v>
+      </c>
+      <c r="P10">
+        <v>2.7590140774220187E-4</v>
+      </c>
+      <c r="Q10">
+        <v>1.7952725712763344E-4</v>
+      </c>
+      <c r="R10">
+        <v>1.6447899039775103E-3</v>
+      </c>
+      <c r="S10">
+        <v>6.4733293674755404E-5</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="0"/>
+        <v>12.58154827798251</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="1"/>
+        <v>0.29327453738582243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>5.64</v>
+      </c>
+      <c r="B11" s="3">
+        <v>18.11</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="D11" s="3">
         <v>11</v>
       </c>
-      <c r="L1" s="1">
-        <v>66</v>
-      </c>
-      <c r="M1" s="1">
-        <v>47</v>
-      </c>
-      <c r="N1">
-        <v>519</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="E11" s="3">
+        <v>16.75</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>5.64</v>
+      </c>
+      <c r="I11" s="3">
+        <v>18.11</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="K11" s="3">
+        <v>11</v>
+      </c>
+      <c r="L11" s="3">
+        <v>16.75</v>
+      </c>
+      <c r="O11">
+        <v>-0.39880209109482384</v>
+      </c>
+      <c r="P11">
+        <v>9.9007508855368468E-3</v>
+      </c>
+      <c r="Q11">
+        <v>1.6447899039775074E-3</v>
+      </c>
+      <c r="R11">
+        <v>0.7781298648332905</v>
+      </c>
+      <c r="S11">
+        <v>-6.4773795602984727E-3</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="0"/>
+        <v>17.098462726583833</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="1"/>
+        <v>0.12142627181823895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="B12" s="3">
+        <v>7.62</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="D12" s="3">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3">
+        <v>24.55</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="3">
+        <v>7.62</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="K12" s="3">
+        <v>16</v>
+      </c>
+      <c r="L12" s="3">
+        <v>24.55</v>
+      </c>
+      <c r="O12">
+        <v>-8.359284529813776E-3</v>
+      </c>
+      <c r="P12">
+        <v>4.0144157359566239E-4</v>
+      </c>
+      <c r="Q12">
+        <v>6.4733293674755621E-5</v>
+      </c>
+      <c r="R12">
+        <v>-6.4773795602984597E-3</v>
+      </c>
+      <c r="S12">
+        <v>6.7383505492302654E-4</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>28.452671507716108</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="1"/>
+        <v>15.230844897139113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>5.41</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11.73</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D13" s="3">
+        <v>18</v>
+      </c>
+      <c r="E13" s="3">
+        <v>27.64</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>5.41</v>
+      </c>
+      <c r="I13" s="3">
+        <v>11.73</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K13" s="3">
+        <v>18</v>
+      </c>
+      <c r="L13" s="3">
+        <v>27.64</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>30.437149817828164</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="1"/>
+        <v>7.8240471033761283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>7.56</v>
+      </c>
+      <c r="B14" s="3">
+        <v>13.85</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D14" s="3">
+        <v>18</v>
+      </c>
+      <c r="E14" s="3">
+        <v>29.64</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7.56</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13.85</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K14" s="3">
+        <v>18</v>
+      </c>
+      <c r="L14" s="3">
+        <v>29.64</v>
+      </c>
+      <c r="N14" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="O14" cm="1">
+        <f t="array" ref="O14:O19">MMULT(TRANSPOSE(G2:L21),L2:L21)</f>
+        <v>467.71999999999997</v>
+      </c>
+      <c r="Q14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="R14" cm="1">
+        <f t="array" ref="R14:R18">MMULT(O8:S12,O14:O18)</f>
+        <v>-2.5405399876210311</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="0"/>
+        <v>28.872762605887885</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="1"/>
+        <v>0.58865321892394906</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="B15" s="3">
+        <v>22.54</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="D15" s="3">
+        <v>20</v>
+      </c>
+      <c r="E15" s="3">
+        <v>32.9</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I15" s="3">
+        <v>22.54</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="K15" s="3">
+        <v>20</v>
+      </c>
+      <c r="L15" s="3">
+        <v>32.9</v>
+      </c>
+      <c r="O15">
+        <v>1023.8301</v>
+      </c>
+      <c r="R15">
+        <v>-0.41974281658067092</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="0"/>
+        <v>34.687532957624349</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>3.1952740745932569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="B16" s="3">
+        <v>7.01</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="D16" s="3">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3">
+        <v>33.520000000000003</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="I16" s="3">
+        <v>7.01</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="K16" s="3">
+        <v>20</v>
+      </c>
+      <c r="L16" s="3">
+        <v>33.520000000000003</v>
+      </c>
+      <c r="O16">
+        <v>9043.8549000000003</v>
+      </c>
+      <c r="R16">
+        <v>2.0899758723689654E-2</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="0"/>
+        <v>34.501474834117069</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="1"/>
+        <v>0.96329285000512144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="D17" s="3">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3">
+        <v>33.75</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="K17" s="3">
+        <v>20</v>
+      </c>
+      <c r="L17" s="3">
+        <v>33.75</v>
+      </c>
+      <c r="O17">
+        <v>287.65010000000001</v>
+      </c>
+      <c r="R17">
+        <v>-2.7163370953309993</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="0"/>
+        <v>34.562469335144868</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="1"/>
+        <v>0.66010642055074453</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="B18" s="3">
+        <v>14.45</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="D18" s="3">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>42.89</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="I18" s="3">
+        <v>14.45</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="K18" s="3">
+        <v>25</v>
+      </c>
+      <c r="L18" s="3">
+        <v>42.89</v>
+      </c>
+      <c r="O18">
+        <v>10039.504999999999</v>
+      </c>
+      <c r="R18">
+        <v>1.9883934461648742</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="0"/>
+        <v>43.405667549512252</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="1"/>
+        <v>0.26591302161997021</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="B19" s="3">
+        <v>50.46</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="D19" s="3">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>48.87</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="I19" s="3">
+        <v>50.46</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="K19" s="3">
+        <v>26</v>
+      </c>
+      <c r="L19" s="3">
+        <v>48.87</v>
+      </c>
+      <c r="O19">
+        <v>17814.938000000002</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="0"/>
+        <v>48.725261946269441</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="1"/>
+        <v>2.094910419770939E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="B20" s="3">
+        <v>24.8</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="D20" s="3">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3">
+        <v>58.45</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="I20" s="3">
+        <v>24.8</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="K20" s="3">
+        <v>30</v>
+      </c>
+      <c r="L20" s="3">
+        <v>58.45</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="0"/>
+        <v>56.387018260658849</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="1"/>
+        <v>4.2558936568550543</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B21" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="D21" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>61.69</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="K21" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="L21" s="3">
+        <v>61.69</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="0"/>
+        <v>57.972153150676007</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="1"/>
+        <v>13.822385195028323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V23" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>65</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>65</v>
-      </c>
-      <c r="K2" s="1">
-        <v>66</v>
-      </c>
-      <c r="L2" s="1">
-        <v>454</v>
-      </c>
-      <c r="M2" s="1">
-        <v>261</v>
-      </c>
-      <c r="N2">
-        <v>3319</v>
-      </c>
-      <c r="P2">
-        <f>$N$9+$N$10*F2+$N$11*G2</f>
-        <v>54.810499624828537</v>
-      </c>
-      <c r="Q2">
-        <f>POWER(H2-P2,2)</f>
-        <v>103.82591789561937</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>38</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>38</v>
-      </c>
-      <c r="K3" s="1">
-        <v>47</v>
-      </c>
-      <c r="L3" s="1">
-        <v>261</v>
-      </c>
-      <c r="M3" s="1">
-        <v>269</v>
-      </c>
-      <c r="N3">
-        <v>2371</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P12" si="0">$N$9+$N$10*F3+$N$11*G3</f>
-        <v>42.746177132655433</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q12" si="1">POWER(H3-P3,2)</f>
-        <v>22.526197374541344</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>5</v>
-      </c>
-      <c r="B4">
+      <c r="W23">
+        <f>AVERAGE(W2:W21)</f>
+        <v>3.1399499954149195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V24" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>51</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>8</v>
-      </c>
-      <c r="H4">
-        <v>51</v>
-      </c>
-      <c r="K4">
-        <v>519</v>
-      </c>
-      <c r="L4">
-        <v>3319</v>
-      </c>
-      <c r="M4">
-        <v>2371</v>
-      </c>
-      <c r="N4">
-        <v>26345</v>
-      </c>
-      <c r="P4">
-        <f t="shared" si="0"/>
-        <v>56.295169344614322</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="1"/>
-        <v>28.038818388143273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>38</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>8</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>38</v>
-      </c>
-      <c r="J5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" cm="1">
-        <f t="array" ref="K5:M7">MINVERSE(K1:M3)</f>
-        <v>1.3973194649279432</v>
-      </c>
-      <c r="L5">
-        <v>-0.14197003803461952</v>
-      </c>
-      <c r="M5">
-        <v>-0.10639343838132949</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="0"/>
-        <v>44.672126057595207</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="1"/>
-        <v>44.517266128440966</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>55</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>55</v>
-      </c>
-      <c r="K6">
-        <v>-0.14197003803461947</v>
-      </c>
-      <c r="L6">
-        <v>1.9405417992703587E-2</v>
-      </c>
-      <c r="M6">
-        <v>5.9768687417527068E-3</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="0"/>
-        <v>57.08424538797891</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>4.3440788373113586</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>43</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>43</v>
-      </c>
-      <c r="K7">
-        <v>-0.10639343838132957</v>
-      </c>
-      <c r="L7">
-        <v>5.976868741752718E-3</v>
-      </c>
-      <c r="M7">
-        <v>1.6507542239126507E-2</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="0"/>
-        <v>41.261507412869634</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="1"/>
-        <v>3.0223564755072347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>25</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>25</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="0"/>
-        <v>21.332557116613586</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="1"/>
-        <v>13.450137302901656</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="C9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-      <c r="H9">
-        <v>33</v>
-      </c>
-      <c r="J9" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" cm="1">
-        <f t="array" ref="K9:K11">MMULT(TRANSPOSE(E2:G12),H2:H12)</f>
-        <v>519</v>
-      </c>
-      <c r="M9" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" cm="1">
-        <f t="array" ref="N9:N11">MMULT(K5:M7,K9:K11)</f>
-        <v>1.7514036585681367</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="0"/>
-        <v>34.092473285207895</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="1"/>
-        <v>1.19349787889293</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>71</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
-      <c r="H10">
-        <v>71</v>
-      </c>
-      <c r="K10">
-        <v>3319</v>
-      </c>
-      <c r="N10">
-        <v>4.8952883645113623</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="0"/>
-        <v>67.222618955212241</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>14.268607557521864</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>51</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>51</v>
-      </c>
-      <c r="K11">
-        <v>2371</v>
-      </c>
-      <c r="N11">
-        <v>3.7584154829361722</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="0"/>
-        <v>46.156795777380999</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="1"/>
-        <v>23.456627141994517</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>49</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>49</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="0"/>
-        <v>53.325829905042738</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="1"/>
-        <v>18.712804367362065</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P14" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q14">
-        <f>AVERAGE(Q2:Q12)</f>
-        <v>25.214209940748784</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P15" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q15">
-        <f>SQRT(Q14)</f>
-        <v>5.0213753037139917</v>
+      <c r="W24">
+        <f>SQRT(W23)</f>
+        <v>1.7719904050008057</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -954,34 +2679,34 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
       <c r="L1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M1" s="1" cm="1">
         <f t="array" ref="M1:Q5">MMULT(TRANSPOSE(F2:J21),F2:J21)</f>
@@ -1000,10 +2725,10 @@
         <v>467.71999999999997</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -1190,16 +2915,16 @@
       <c r="J5">
         <v>6.91</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5">
         <v>467.71999999999997</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5">
         <v>1023.8301000000001</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5">
         <v>9043.8549000000003</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5">
         <v>287.65010000000001</v>
       </c>
       <c r="Q5">
@@ -1317,7 +3042,7 @@
         <v>4.18</v>
       </c>
       <c r="L8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M8" cm="1">
         <f t="array" ref="M8:P11">MINVERSE(M1:P4)</f>
@@ -1591,14 +3316,14 @@
         <v>16.75</v>
       </c>
       <c r="L14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M14" cm="1">
         <f t="array" ref="M14:M18">MMULT(TRANSPOSE(F2:J21),J2:J21)</f>
         <v>467.71999999999997</v>
       </c>
       <c r="O14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P14" cm="1">
         <f t="array" ref="P14:P17">MMULT(M8:P11,M14:M17)</f>
@@ -1895,7 +3620,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="S23" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <f>AVERAGE(T2:T21)</f>
@@ -1904,7 +3629,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="S24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <f>SQRT(T23)</f>
